--- a/docs/d/02/inyear.xlsx
+++ b/docs/d/02/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 92 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 90 clubs short</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2847,8 +2847,8 @@
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
@@ -6489,7 +6489,7 @@
         <v>0</v>
       </c>
       <c r="Q57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57" s="9" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6598,8 +6598,8 @@
       <c r="S58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T58" s="9" t="n">
-        <v>0</v>
+      <c r="T58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U58" s="9" t="n">
         <v>0</v>
@@ -8588,13 +8588,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L78" s="8" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -14787,7 +14787,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14857,8 +14857,8 @@
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA139" s="10" t="n">
         <v>1</v>
@@ -21802,7 +21802,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -22033,7 +22033,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -22594,7 +22594,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>

--- a/docs/d/02/inyear.xlsx
+++ b/docs/d/02/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,11 @@
       <c r="AB18" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC18" s="4" t="inlineStr"/>
+      <c r="AC18" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -7029,7 +7033,11 @@
       <c r="AB62" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC62" s="4" t="inlineStr"/>
+      <c r="AC62" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -9158,7 +9166,11 @@
       <c r="AB83" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC83" s="4" t="inlineStr"/>
+      <c r="AC83" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -9259,7 +9271,11 @@
       <c r="AB84" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC84" s="4" t="inlineStr"/>
+      <c r="AC84" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -9360,7 +9376,11 @@
       <c r="AB85" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC85" s="4" t="inlineStr"/>
+      <c r="AC85" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -10378,7 +10398,11 @@
       <c r="AB95" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC95" s="4" t="inlineStr"/>
+      <c r="AC95" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -11392,7 +11416,11 @@
       <c r="AB105" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC105" s="4" t="inlineStr"/>
+      <c r="AC105" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -20352,7 +20380,11 @@
       <c r="AB193" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC193" s="4" t="inlineStr"/>
+      <c r="AC193" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
@@ -20554,7 +20586,11 @@
       <c r="AB195" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC195" s="4" t="inlineStr"/>
+      <c r="AC195" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">

--- a/docs/d/02/inyear.xlsx
+++ b/docs/d/02/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 24 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 24 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 85 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 57 clubs short</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1120,8 +1120,8 @@
       <c r="Y4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" s="9" t="n">
-        <v>0</v>
+      <c r="Z4" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA4" s="10" t="n">
         <v>1</v>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2224,8 +2224,8 @@
       <c r="T15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U15" s="9" t="n">
-        <v>0</v>
+      <c r="U15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V15" s="9" t="n">
         <v>0</v>
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="P19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="9" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3059,8 +3059,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3261,8 +3261,8 @@
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3871,8 +3871,8 @@
       <c r="Y31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="9" t="n">
-        <v>0</v>
+      <c r="Z31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>1</v>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5095,8 +5095,8 @@
       <c r="Y43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z43" s="9" t="n">
-        <v>0</v>
+      <c r="Z43" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA43" s="10" t="n">
         <v>1</v>
@@ -5167,10 +5167,10 @@
         </is>
       </c>
       <c r="P44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" s="9" t="n">
         <v>0</v>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6016,8 +6016,8 @@
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
@@ -7230,8 +7230,8 @@
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA64" s="9" t="n">
         <v>0</v>
@@ -7261,7 +7261,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7302,16 +7302,16 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" s="9" t="n">
         <v>0</v>
@@ -7331,8 +7331,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7735,8 +7735,8 @@
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="9" t="n">
-        <v>0</v>
+      <c r="Z69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA69" s="10" t="n">
         <v>1</v>
@@ -8069,7 +8069,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8139,8 +8139,8 @@
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
@@ -8376,7 +8376,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="P76" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q76" s="10" t="n">
         <v>2</v>
@@ -8428,8 +8428,8 @@
       <c r="S76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T76" s="9" t="n">
-        <v>0</v>
+      <c r="T76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U76" s="9" t="n">
         <v>0</v>
@@ -9559,7 +9559,7 @@
         <v>1</v>
       </c>
       <c r="U87" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V87" s="9" t="n">
         <v>2</v>
@@ -9952,7 +9952,7 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>1</v>
@@ -10288,8 +10288,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="9" t="n">
         <v>0</v>
@@ -12969,7 +12969,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13039,8 +13039,8 @@
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="9" t="n">
-        <v>0</v>
+      <c r="Z121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA121" s="10" t="n">
         <v>1</v>
@@ -13373,7 +13373,7 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Kent Evening Toastmasters Club</t>
+          <t>Kent Evening Toastmasters</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
@@ -13583,7 +13583,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13653,8 +13653,8 @@
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="9" t="n">
-        <v>0</v>
+      <c r="Z127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
@@ -13785,7 +13785,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13828,11 +13828,11 @@
       <c r="P129" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q129" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R129" s="9" t="n">
-        <v>0</v>
+      <c r="Q129" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R129" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S129" s="9" t="n">
         <v>1</v>
@@ -13890,7 +13890,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13960,8 +13960,8 @@
       <c r="Y130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z130" s="9" t="n">
-        <v>0</v>
+      <c r="Z130" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA130" s="10" t="n">
         <v>1</v>
@@ -13991,7 +13991,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14041,7 +14041,7 @@
         <v>0</v>
       </c>
       <c r="S131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T131" s="9" t="n">
         <v>0</v>
@@ -14061,8 +14061,8 @@
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="9" t="n">
-        <v>0</v>
+      <c r="Z131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA131" s="10" t="n">
         <v>1</v>
@@ -14399,7 +14399,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14451,8 +14451,8 @@
       <c r="S135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T135" s="9" t="n">
-        <v>0</v>
+      <c r="T135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U135" s="9" t="n">
         <v>0</v>
@@ -14815,7 +14815,7 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14858,8 +14858,8 @@
       <c r="P139" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q139" s="9" t="n">
-        <v>1</v>
+      <c r="Q139" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R139" s="9" t="n">
         <v>0</v>
@@ -15530,7 +15530,7 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -15585,8 +15585,8 @@
       <c r="T146" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U146" s="9" t="n">
-        <v>0</v>
+      <c r="U146" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V146" s="9" t="n">
         <v>2</v>
@@ -15675,7 +15675,7 @@
         <v>0</v>
       </c>
       <c r="Q147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R147" s="9" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15806,8 +15806,8 @@
       <c r="Y148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z148" s="9" t="n">
-        <v>0</v>
+      <c r="Z148" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA148" s="10" t="n">
         <v>1</v>
@@ -16140,7 +16140,7 @@
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>10</v>
@@ -16210,8 +16210,8 @@
       <c r="Y152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z152" s="9" t="n">
-        <v>0</v>
+      <c r="Z152" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA152" s="10" t="n">
         <v>1</v>
@@ -16241,7 +16241,7 @@
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -16311,8 +16311,8 @@
       <c r="Y153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z153" s="9" t="n">
-        <v>0</v>
+      <c r="Z153" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA153" s="10" t="n">
         <v>1</v>
@@ -16342,7 +16342,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -16412,8 +16412,8 @@
       <c r="Y154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z154" s="9" t="n">
-        <v>0</v>
+      <c r="Z154" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA154" s="10" t="n">
         <v>1</v>
@@ -16544,7 +16544,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -16614,8 +16614,8 @@
       <c r="Y156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z156" s="9" t="n">
-        <v>0</v>
+      <c r="Z156" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA156" s="10" t="n">
         <v>1</v>
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -17123,8 +17123,8 @@
       <c r="Y161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z161" s="9" t="n">
-        <v>0</v>
+      <c r="Z161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA161" s="10" t="n">
         <v>1</v>
@@ -17360,7 +17360,7 @@
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -17403,8 +17403,8 @@
       <c r="P164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" s="9" t="n">
-        <v>1</v>
+      <c r="Q164" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R164" s="9" t="n">
         <v>0</v>
@@ -17430,8 +17430,8 @@
       <c r="Y164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z164" s="9" t="n">
-        <v>0</v>
+      <c r="Z164" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA164" s="10" t="n">
         <v>1</v>
@@ -17562,7 +17562,7 @@
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F166" s="6" t="n">
         <v>10</v>
@@ -17632,8 +17632,8 @@
       <c r="Y166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z166" s="9" t="n">
-        <v>0</v>
+      <c r="Z166" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA166" s="10" t="n">
         <v>1</v>
@@ -17764,7 +17764,7 @@
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>10</v>
@@ -17834,8 +17834,8 @@
       <c r="Y168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z168" s="9" t="n">
-        <v>0</v>
+      <c r="Z168" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA168" s="10" t="n">
         <v>1</v>
@@ -17906,7 +17906,7 @@
         </is>
       </c>
       <c r="P169" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q169" s="10" t="n">
         <v>2</v>
@@ -18277,7 +18277,7 @@
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F173" s="6" t="n">
         <v>10</v>
@@ -18329,8 +18329,8 @@
       <c r="S173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T173" s="9" t="n">
-        <v>0</v>
+      <c r="T173" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U173" s="9" t="n">
         <v>0</v>
@@ -18685,7 +18685,7 @@
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -18755,8 +18755,8 @@
       <c r="Y177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z177" s="9" t="n">
-        <v>0</v>
+      <c r="Z177" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA177" s="10" t="n">
         <v>1</v>
@@ -18887,7 +18887,7 @@
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -18957,8 +18957,8 @@
       <c r="Y179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z179" s="9" t="n">
-        <v>0</v>
+      <c r="Z179" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA179" s="10" t="n">
         <v>1</v>
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F184" s="6" t="n">
         <v>10</v>
@@ -19462,8 +19462,8 @@
       <c r="Y184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z184" s="9" t="n">
-        <v>0</v>
+      <c r="Z184" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA184" s="10" t="n">
         <v>1</v>
@@ -20406,7 +20406,7 @@
         </is>
       </c>
       <c r="E194" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F194" s="6" t="n">
         <v>10</v>
@@ -20476,8 +20476,8 @@
       <c r="Y194" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z194" s="9" t="n">
-        <v>0</v>
+      <c r="Z194" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA194" s="10" t="n">
         <v>1</v>
@@ -21234,7 +21234,7 @@
         </is>
       </c>
       <c r="E202" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F202" s="6" t="n">
         <v>10</v>
@@ -21286,8 +21286,8 @@
       <c r="S202" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T202" s="9" t="n">
-        <v>0</v>
+      <c r="T202" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U202" s="9" t="n">
         <v>0</v>
@@ -21706,7 +21706,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -21772,7 +21772,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -21838,7 +21838,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -21904,7 +21904,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -21970,7 +21970,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -22003,7 +22003,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -22102,7 +22102,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -22135,7 +22135,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -22168,7 +22168,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -22465,7 +22465,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -22498,7 +22498,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -22531,13 +22531,13 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -22564,7 +22564,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -22597,7 +22597,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -22630,7 +22630,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -22663,7 +22663,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -22696,7 +22696,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -22729,7 +22729,7 @@
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -22762,7 +22762,7 @@
         <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>0.83</v>
+        <v>1.5</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -22795,7 +22795,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -22828,7 +22828,7 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -22861,7 +22861,7 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -22894,7 +22894,7 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -22960,7 +22960,7 @@
         <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -23026,7 +23026,7 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>

--- a/docs/d/02/inyear.xlsx
+++ b/docs/d/02/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 24 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 24 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 57 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 57 clubs short</t>
         </is>
       </c>
     </row>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1876,13 +1876,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1977,13 +1977,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="P16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>0</v>
@@ -2322,8 +2322,8 @@
       <c r="S16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T16" s="9" t="n">
-        <v>0</v>
+      <c r="T16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U16" s="9" t="n">
         <v>0</v>
@@ -2385,17 +2385,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M17" s="8" t="n">
@@ -2430,7 +2430,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2490,17 +2490,17 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M18" s="8" t="n">
@@ -2535,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2595,13 +2595,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2639,8 +2639,8 @@
       <c r="U19" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V19" s="9" t="n">
-        <v>2</v>
+      <c r="V19" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2696,13 +2696,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2797,13 +2797,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2902,13 +2902,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -3003,13 +3003,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" s="9" t="n">
         <v>0</v>
@@ -3104,13 +3104,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3205,13 +3205,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3232,16 +3232,16 @@
         </is>
       </c>
       <c r="P25" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" s="9" t="n">
         <v>0</v>
@@ -3306,13 +3306,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3407,13 +3407,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3508,13 +3508,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>0</v>
@@ -3613,13 +3613,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3714,13 +3714,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3916,17 +3916,17 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M32" s="8" t="n">
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="P32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="9" t="n">
         <v>0</v>
@@ -3954,8 +3954,8 @@
       <c r="S32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T32" s="9" t="n">
-        <v>0</v>
+      <c r="T32" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U32" s="9" t="n">
         <v>0</v>
@@ -4021,13 +4021,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4324,13 +4324,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>1</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" s="9" t="n">
         <v>0</v>
@@ -4369,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4425,13 +4425,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4526,13 +4526,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4627,13 +4627,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4728,13 +4728,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4833,13 +4833,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4934,17 +4934,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M42" s="8" t="n">
@@ -4970,7 +4970,7 @@
         <v>0</v>
       </c>
       <c r="S42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" s="9" t="n">
         <v>0</v>
@@ -5039,17 +5039,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M43" s="8" t="n">
@@ -5140,13 +5140,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5241,13 +5241,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5342,13 +5342,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5447,13 +5447,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5552,13 +5552,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5758,13 +5758,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5859,13 +5859,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>4</v>
       </c>
       <c r="W52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X52" s="10" t="n">
         <v>4</v>
@@ -6061,13 +6061,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6263,13 +6263,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6465,13 +6465,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6509,11 +6509,11 @@
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="9" t="n">
-        <v>0</v>
+      <c r="V57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X57" s="9" t="n">
         <v>0</v>
@@ -6564,13 +6564,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6665,13 +6665,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6766,13 +6766,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
@@ -6867,13 +6867,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6968,13 +6968,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7073,13 +7073,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7174,13 +7174,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7376,13 +7376,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7477,13 +7477,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7578,13 +7578,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>4</v>
       </c>
       <c r="W68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X68" s="9" t="n">
         <v>0</v>
@@ -7679,13 +7679,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7780,17 +7780,17 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-26</v>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M70" s="8" t="n">
@@ -7881,17 +7881,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-19</v>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M71" s="8" t="n">
@@ -7982,13 +7982,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8083,17 +8083,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8188,13 +8188,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>0</v>
       </c>
       <c r="Q74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" s="9" t="n">
         <v>0</v>
@@ -8232,8 +8232,8 @@
       <c r="U74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V74" s="9" t="n">
-        <v>2</v>
+      <c r="V74" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8289,13 +8289,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8390,13 +8390,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8495,13 +8495,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>0</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8596,13 +8596,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8697,13 +8697,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8798,13 +8798,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8899,13 +8899,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9000,13 +9000,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9101,17 +9101,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-21</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -9206,17 +9206,17 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M84" s="8" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9416,13 +9416,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9517,17 +9517,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M87" s="8" t="n">
@@ -9622,13 +9622,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9723,13 +9723,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9824,13 +9824,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9925,13 +9925,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -9952,10 +9952,10 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q91" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="Q91" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
@@ -10030,13 +10030,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -10131,13 +10131,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10158,7 +10158,7 @@
         </is>
       </c>
       <c r="P93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q93" s="9" t="n">
         <v>0</v>
@@ -10232,13 +10232,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10333,13 +10333,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -10424,7 +10424,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10438,17 +10438,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L96" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M96" s="8" t="n">
@@ -10479,11 +10479,11 @@
       <c r="T96" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V96" s="9" t="n">
-        <v>2</v>
+      <c r="U96" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V96" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10640,13 +10640,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>0</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10745,13 +10745,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10846,13 +10846,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10947,13 +10947,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -11149,13 +11149,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -11351,13 +11351,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>4</v>
       </c>
       <c r="W105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>7</v>
@@ -11456,13 +11456,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11557,13 +11557,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11658,13 +11658,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11810,8 +11810,8 @@
       <c r="V109" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W109" s="9" t="n">
-        <v>1</v>
+      <c r="W109" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X109" s="9" t="n">
         <v>0</v>
@@ -11864,13 +11864,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11965,17 +11965,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -12070,13 +12070,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -12171,13 +12171,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12272,13 +12272,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>1</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -12373,13 +12373,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12474,13 +12474,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12575,13 +12575,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>4</v>
       </c>
       <c r="W120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X120" s="10" t="n">
         <v>5</v>
@@ -12983,13 +12983,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -13084,13 +13084,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13185,13 +13185,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
@@ -13391,17 +13391,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L125" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M125" s="8" t="n">
@@ -13496,13 +13496,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13597,13 +13597,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13736,8 +13736,8 @@
       <c r="S128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T128" s="9" t="n">
-        <v>0</v>
+      <c r="T128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U128" s="9" t="n">
         <v>0</v>
@@ -13799,17 +13799,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L129" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M129" s="8" t="n">
@@ -13890,7 +13890,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13904,13 +13904,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -13948,8 +13948,8 @@
       <c r="U130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V130" s="9" t="n">
-        <v>2</v>
+      <c r="V130" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
@@ -14005,13 +14005,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14110,13 +14110,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14211,13 +14211,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -14312,13 +14312,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -14413,13 +14413,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -14518,13 +14518,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>0</v>
       </c>
       <c r="V136" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -14623,13 +14623,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>0</v>
       </c>
       <c r="Q137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R137" s="9" t="n">
         <v>0</v>
@@ -14671,7 +14671,7 @@
         <v>4</v>
       </c>
       <c r="W137" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X137" s="10" t="n">
         <v>7</v>
@@ -14728,13 +14728,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14829,13 +14829,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>0</v>
       </c>
       <c r="S139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T139" s="9" t="n">
         <v>0</v>
@@ -14874,7 +14874,7 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -15031,13 +15031,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -15076,7 +15076,7 @@
         <v>0</v>
       </c>
       <c r="V141" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
@@ -15237,13 +15237,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>0</v>
       </c>
       <c r="V144" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W144" s="9" t="n">
         <v>0</v>
@@ -15439,13 +15439,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -15645,13 +15645,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15750,13 +15750,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -15786,13 +15786,13 @@
         <v>0</v>
       </c>
       <c r="S148" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T148" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T148" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U148" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V148" s="9" t="n">
         <v>2</v>
@@ -15851,13 +15851,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>0</v>
       </c>
       <c r="V149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W149" s="9" t="n">
         <v>0</v>
@@ -15952,13 +15952,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
@@ -16053,13 +16053,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -16154,13 +16154,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -16255,13 +16255,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         <v>0</v>
       </c>
       <c r="V153" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W153" s="9" t="n">
         <v>0</v>
@@ -16356,13 +16356,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L154" s="7" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>0</v>
       </c>
       <c r="V155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W155" s="9" t="n">
         <v>0</v>
@@ -16558,13 +16558,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -16659,17 +16659,17 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L157" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L157" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M157" s="8" t="n">
@@ -16764,13 +16764,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L158" s="7" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>0</v>
       </c>
       <c r="V158" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W158" s="9" t="n">
         <v>0</v>
@@ -16865,13 +16865,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
@@ -16910,7 +16910,7 @@
         <v>0</v>
       </c>
       <c r="V159" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W159" s="9" t="n">
         <v>0</v>
@@ -16966,13 +16966,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L160" s="7" t="inlineStr">
         <is>
@@ -17067,13 +17067,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>0</v>
       </c>
       <c r="V161" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W161" s="9" t="n">
         <v>0</v>
@@ -17172,17 +17172,17 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L162" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-32</v>
+      </c>
+      <c r="L162" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M162" s="8" t="n">
@@ -17259,7 +17259,7 @@
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -17317,8 +17317,8 @@
       <c r="U163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V163" s="9" t="n">
-        <v>2</v>
+      <c r="V163" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W163" s="9" t="n">
         <v>0</v>
@@ -17374,13 +17374,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -17475,13 +17475,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
@@ -17576,13 +17576,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -17677,13 +17677,13 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
@@ -17778,17 +17778,17 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L168" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L168" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M168" s="8" t="n">
@@ -17805,7 +17805,7 @@
         </is>
       </c>
       <c r="P168" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q168" s="9" t="n">
         <v>0</v>
@@ -17879,13 +17879,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
@@ -17980,17 +17980,17 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L170" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L170" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M170" s="8" t="n">
@@ -18085,13 +18085,13 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
@@ -18190,13 +18190,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L172" s="7" t="inlineStr">
         <is>
@@ -18291,13 +18291,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>0</v>
       </c>
       <c r="V173" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W173" s="9" t="n">
         <v>0</v>
@@ -18392,13 +18392,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L174" s="7" t="inlineStr">
         <is>
@@ -18493,13 +18493,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
@@ -18598,13 +18598,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L176" s="7" t="inlineStr">
         <is>
@@ -18699,13 +18699,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
@@ -18800,13 +18800,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L178" s="7" t="inlineStr">
         <is>
@@ -18901,13 +18901,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
@@ -19002,13 +19002,13 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J180" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L180" s="7" t="inlineStr">
         <is>
@@ -19103,13 +19103,13 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
@@ -19204,13 +19204,13 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L182" s="7" t="inlineStr">
         <is>
@@ -19305,13 +19305,13 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L183" s="7" t="inlineStr">
         <is>
@@ -19406,13 +19406,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L184" s="7" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>0</v>
       </c>
       <c r="V184" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W184" s="9" t="n">
         <v>0</v>
@@ -19507,13 +19507,13 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
@@ -19608,13 +19608,13 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L186" s="7" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>0</v>
       </c>
       <c r="V186" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W186" s="9" t="n">
         <v>0</v>
@@ -19709,13 +19709,13 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J187" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L187" s="7" t="inlineStr">
         <is>
@@ -19911,13 +19911,13 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J189" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
@@ -20012,13 +20012,13 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L190" s="7" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>0</v>
       </c>
       <c r="S190" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T190" s="9" t="n">
         <v>0</v>
@@ -20113,13 +20113,13 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>0</v>
       </c>
       <c r="V191" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W191" s="9" t="n">
         <v>0</v>
@@ -20214,13 +20214,13 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J192" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L192" s="7" t="inlineStr">
         <is>
@@ -20315,17 +20315,17 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J193" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L193" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L193" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M193" s="8" t="n">
@@ -20420,13 +20420,13 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L194" s="7" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>0</v>
       </c>
       <c r="V194" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W194" s="9" t="n">
         <v>0</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J195" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="L195" s="4" t="inlineStr">
         <is>
@@ -20626,13 +20626,13 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J196" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L196" s="7" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         </is>
       </c>
       <c r="P196" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q196" s="9" t="n">
         <v>0</v>
@@ -20671,7 +20671,7 @@
         <v>0</v>
       </c>
       <c r="V196" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W196" s="9" t="n">
         <v>0</v>
@@ -20731,13 +20731,13 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J197" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
@@ -20832,13 +20832,13 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J198" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L198" s="7" t="inlineStr">
         <is>
@@ -20937,13 +20937,13 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J199" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K199" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
@@ -21042,13 +21042,13 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J200" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K200" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L200" s="7" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>0</v>
       </c>
       <c r="S200" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T200" s="10" t="n">
         <v>1</v>
@@ -21143,17 +21143,17 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L201" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L201" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M201" s="8" t="n">
@@ -21234,7 +21234,7 @@
         </is>
       </c>
       <c r="E202" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F202" s="6" t="n">
         <v>10</v>
@@ -21248,13 +21248,13 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K202" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L202" s="7" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         </is>
       </c>
       <c r="P202" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q202" s="10" t="n">
         <v>2</v>
@@ -21289,11 +21289,11 @@
       <c r="T202" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U202" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V202" s="9" t="n">
-        <v>3</v>
+      <c r="U202" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V202" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W202" s="9" t="n">
         <v>0</v>
@@ -21349,13 +21349,13 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K203" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L203" s="7" t="inlineStr">
         <is>
@@ -21450,13 +21450,13 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K204" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L204" s="7" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>0</v>
       </c>
       <c r="V204" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W204" s="9" t="n">
         <v>0</v>
@@ -21551,13 +21551,13 @@
         </is>
       </c>
       <c r="I205" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J205" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K205" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L205" s="7" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -21820,7 +21820,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -21904,7 +21904,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -21919,7 +21919,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -21985,7 +21985,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -22036,7 +22036,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -22150,7 +22150,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -22168,7 +22168,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -22216,7 +22216,7 @@
         <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -22249,7 +22249,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -22267,7 +22267,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -22300,13 +22300,13 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -22315,7 +22315,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -22366,7 +22366,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -22414,7 +22414,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -22498,7 +22498,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -22513,7 +22513,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -22531,7 +22531,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -22546,7 +22546,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -22630,7 +22630,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -22711,7 +22711,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -22744,7 +22744,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -22762,7 +22762,7 @@
         <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -22777,7 +22777,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -22810,7 +22810,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -22975,7 +22975,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -23026,13 +23026,13 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -23041,7 +23041,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/02/inyear.xlsx
+++ b/docs/d/02/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/02/inyear.xlsx
+++ b/docs/d/02/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/02/inyear.xlsx
+++ b/docs/d/02/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/02/inyear.xlsx
+++ b/docs/d/02/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/02/inyear.xlsx
+++ b/docs/d/02/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 24 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 24 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 57 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 58 clubs short</t>
         </is>
       </c>
     </row>
@@ -1977,13 +1977,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2385,13 +2385,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2490,13 +2490,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2696,13 +2696,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2835,8 +2835,8 @@
       <c r="S21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T21" s="9" t="n">
-        <v>0</v>
+      <c r="T21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U21" s="9" t="n">
         <v>0</v>
@@ -3815,13 +3815,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="P42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q42" s="9" t="n">
         <v>0</v>
@@ -5039,13 +5039,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>0</v>
       </c>
       <c r="S43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" s="9" t="n">
         <v>0</v>
@@ -6766,13 +6766,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6867,13 +6867,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6995,10 +6995,10 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q62" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="R62" s="9" t="n">
         <v>0</v>
@@ -7073,13 +7073,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>0</v>
       </c>
       <c r="Q63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" s="9" t="n">
         <v>0</v>
@@ -7174,13 +7174,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -7881,13 +7881,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -8188,13 +8188,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8289,13 +8289,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q77" s="9" t="n">
         <v>1</v>
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9723,13 +9723,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9925,13 +9925,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>4</v>
       </c>
       <c r="W91" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X91" s="10" t="n">
         <v>7</v>
@@ -10131,13 +10131,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10333,13 +10333,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -10438,13 +10438,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q96" s="9" t="n">
         <v>0</v>
@@ -10486,7 +10486,7 @@
         <v>4</v>
       </c>
       <c r="W96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X96" s="10" t="n">
         <v>6</v>
@@ -10626,7 +10626,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10640,13 +10640,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10684,8 +10684,8 @@
       <c r="U98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V98" s="9" t="n">
-        <v>3</v>
+      <c r="V98" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -11048,13 +11048,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11149,13 +11149,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11205,8 +11205,8 @@
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="10" t="n">
-        <v>1</v>
+      <c r="Z103" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -11351,13 +11351,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>0</v>
       </c>
       <c r="S105" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T105" s="10" t="n">
         <v>1</v>
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11965,13 +11965,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -12171,13 +12171,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12373,13 +12373,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         </is>
       </c>
       <c r="P126" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q126" s="10" t="n">
         <v>2</v>
@@ -13799,13 +13799,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13930,8 +13930,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P130" s="9" t="n">
-        <v>3</v>
+      <c r="P130" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q130" s="9" t="n">
         <v>1</v>
@@ -14005,13 +14005,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14728,13 +14728,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -15237,13 +15237,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
@@ -15544,13 +15544,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L146" s="7" t="inlineStr">
         <is>
@@ -15645,13 +15645,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>1</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
@@ -16659,13 +16659,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -16764,13 +16764,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L158" s="7" t="inlineStr">
         <is>
@@ -16865,13 +16865,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>10</v>
@@ -17172,17 +17172,17 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>-32</v>
-      </c>
-      <c r="L162" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L162" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M162" s="8" t="n">
@@ -17216,8 +17216,8 @@
       <c r="U162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V162" s="9" t="n">
-        <v>0</v>
+      <c r="V162" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W162" s="9" t="n">
         <v>0</v>
@@ -17576,13 +17576,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -19002,13 +19002,13 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J180" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L180" s="7" t="inlineStr">
         <is>
@@ -19305,13 +19305,13 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L183" s="7" t="inlineStr">
         <is>
@@ -20012,13 +20012,13 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L190" s="7" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         </is>
       </c>
       <c r="E191" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F191" s="6" t="n">
         <v>10</v>
@@ -20113,13 +20113,13 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
@@ -20142,8 +20142,8 @@
       <c r="P191" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q191" s="9" t="n">
-        <v>1</v>
+      <c r="Q191" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R191" s="9" t="n">
         <v>0</v>
@@ -20345,7 +20345,7 @@
         <v>2</v>
       </c>
       <c r="Q193" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R193" s="9" t="n">
         <v>0</v>
@@ -20507,7 +20507,7 @@
         </is>
       </c>
       <c r="E195" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F195" s="6" t="n">
         <v>10</v>
@@ -20556,8 +20556,8 @@
       <c r="R195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S195" s="9" t="n">
-        <v>1</v>
+      <c r="S195" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T195" s="10" t="n">
         <v>1</v>
@@ -20653,7 +20653,7 @@
         </is>
       </c>
       <c r="P196" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q196" s="9" t="n">
         <v>0</v>
@@ -20832,13 +20832,13 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J198" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L198" s="7" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>1</v>
       </c>
       <c r="U200" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V200" s="10" t="n">
         <v>4</v>
@@ -21436,7 +21436,7 @@
         </is>
       </c>
       <c r="E204" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F204" s="6" t="n">
         <v>10</v>
@@ -21488,8 +21488,8 @@
       <c r="S204" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T204" s="9" t="n">
-        <v>0</v>
+      <c r="T204" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U204" s="9" t="n">
         <v>0</v>
@@ -21838,7 +21838,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -22069,7 +22069,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -22300,7 +22300,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -22333,7 +22333,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -22531,7 +22531,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -22729,7 +22729,7 @@
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -22744,7 +22744,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -22927,7 +22927,7 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -22960,7 +22960,7 @@
         <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -23026,7 +23026,7 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>

--- a/docs/d/02/inyear.xlsx
+++ b/docs/d/02/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:49 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 24 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 24 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 58 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 58 clubs short</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="9" t="n">
         <v>0</v>
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -2078,13 +2078,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2385,13 +2385,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>0</v>
@@ -3003,13 +3003,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3613,13 +3613,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -7679,13 +7679,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -8188,13 +8188,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>2</v>
       </c>
       <c r="R76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S76" s="9" t="n">
         <v>0</v>
@@ -8596,13 +8596,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -9206,13 +9206,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9517,17 +9517,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L87" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-3</v>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M87" s="8" t="n">
@@ -9562,7 +9562,7 @@
         <v>2</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9925,13 +9925,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>4</v>
       </c>
       <c r="W91" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X91" s="10" t="n">
         <v>7</v>
@@ -10438,13 +10438,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>4</v>
       </c>
       <c r="W96" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X96" s="10" t="n">
         <v>6</v>
@@ -11965,13 +11965,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
@@ -12258,7 +12258,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12272,13 +12272,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12316,8 +12316,8 @@
       <c r="U114" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V114" s="9" t="n">
-        <v>3</v>
+      <c r="V114" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -12575,13 +12575,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -13185,13 +13185,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
@@ -13799,17 +13799,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L129" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L129" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M129" s="8" t="n">
@@ -13847,7 +13847,7 @@
         <v>4</v>
       </c>
       <c r="W129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X129" s="10" t="n">
         <v>7</v>
@@ -13890,7 +13890,7 @@
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13904,13 +13904,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -13933,8 +13933,8 @@
       <c r="P130" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q130" s="9" t="n">
-        <v>1</v>
+      <c r="Q130" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R130" s="9" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
         <v>4</v>
       </c>
       <c r="W130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X130" s="10" t="n">
         <v>5</v>
@@ -14440,7 +14440,7 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q135" s="9" t="n">
         <v>0</v>
@@ -14609,7 +14609,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14650,22 +14650,22 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q137" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q137" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R137" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S137" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T137" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U137" s="9" t="n">
-        <v>0</v>
+      <c r="U137" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V137" s="10" t="n">
         <v>4</v>
@@ -15031,13 +15031,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -15076,7 +15076,7 @@
         <v>0</v>
       </c>
       <c r="V141" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
@@ -15439,13 +15439,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -16154,13 +16154,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -16764,13 +16764,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L158" s="7" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>0</v>
       </c>
       <c r="V158" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W158" s="9" t="n">
         <v>0</v>
@@ -17374,13 +17374,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>0</v>
       </c>
       <c r="V164" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W164" s="9" t="n">
         <v>0</v>
@@ -17576,13 +17576,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F170" s="6" t="n">
         <v>10</v>
@@ -17980,13 +17980,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L170" s="7" t="inlineStr">
         <is>
@@ -18024,8 +18024,8 @@
       <c r="U170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V170" s="9" t="n">
-        <v>3</v>
+      <c r="V170" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W170" s="9" t="n">
         <v>0</v>
@@ -18217,7 +18217,7 @@
         </is>
       </c>
       <c r="P172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q172" s="9" t="n">
         <v>1</v>
@@ -19204,13 +19204,13 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L182" s="7" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>0</v>
       </c>
       <c r="S185" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T185" s="9" t="n">
         <v>0</v>
@@ -20012,13 +20012,13 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L190" s="7" t="inlineStr">
         <is>
@@ -21143,13 +21143,13 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L201" s="7" t="inlineStr">
         <is>
@@ -21188,7 +21188,7 @@
         <v>0</v>
       </c>
       <c r="V201" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W201" s="9" t="n">
         <v>0</v>
@@ -21436,7 +21436,7 @@
         </is>
       </c>
       <c r="E204" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F204" s="6" t="n">
         <v>10</v>
@@ -21450,13 +21450,13 @@
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K204" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L204" s="7" t="inlineStr">
         <is>
@@ -21494,11 +21494,11 @@
       <c r="U204" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V204" s="9" t="n">
-        <v>3</v>
+      <c r="V204" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W204" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X204" s="9" t="n">
         <v>2</v>
@@ -21551,13 +21551,13 @@
         </is>
       </c>
       <c r="I205" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J205" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K205" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L205" s="7" t="inlineStr">
         <is>
@@ -22249,7 +22249,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -22399,7 +22399,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -22531,7 +22531,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -22546,7 +22546,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -22564,13 +22564,13 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -22795,7 +22795,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -23026,7 +23026,7 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
